--- a/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
   <si>
     <t>RGC</t>
   </si>
@@ -656,71 +656,83 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -757,8 +769,17 @@
       <c r="N8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -795,8 +816,17 @@
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -833,8 +863,17 @@
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -849,46 +888,58 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>500</v>
+      </c>
+      <c r="E12" s="3">
+        <v>200</v>
+      </c>
+      <c r="F12" s="3">
         <v>1400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H12" s="3">
         <v>1100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="J12" s="3">
         <v>300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="K12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="L12" s="3">
         <v>200</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -925,8 +976,17 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -963,8 +1023,17 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1001,8 +1070,17 @@
       <c r="N15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1014,46 +1092,58 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F17" s="3">
+        <v>3400</v>
+      </c>
+      <c r="G17" s="3">
         <v>4000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>3700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>1400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="K17" s="3">
         <v>800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>300</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1061,37 +1151,46 @@
         <v>3</v>
       </c>
       <c r="E18" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F18" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="H18" s="3">
         <v>-3700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>-1400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>-400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>-800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-300</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1205,11 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1115,10 +1217,10 @@
         <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1129,14 +1231,14 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
@@ -1144,8 +1246,17 @@
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1155,35 +1266,44 @@
       <c r="E21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="3">
+      <c r="F21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I21" s="3">
         <v>-1300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="J21" s="3">
         <v>-300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="K21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1220,46 +1340,64 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F23" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-3900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>-3700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>-1300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>-300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>-800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1296,8 +1434,17 @@
       <c r="N24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1334,84 +1481,111 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="F26" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-3900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>-3700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>-1300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>-300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>-800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F27" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="G27" s="3">
         <v>-3900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>-3600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="I27" s="3">
         <v>-1300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="J27" s="3">
         <v>-300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3">
         <v>-800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1448,8 +1622,17 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1486,8 +1669,17 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1524,8 +1716,17 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1562,8 +1763,17 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1571,10 +1781,10 @@
         <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -1585,14 +1795,14 @@
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
@@ -1600,46 +1810,64 @@
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F33" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="G33" s="3">
         <v>-3900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>-3600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>-1300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>-300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
         <v>-800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1676,89 +1904,116 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F35" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="G35" s="3">
         <v>-3900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>-3600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>-1300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>-300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
         <v>-800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1773,8 +2028,11 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1789,32 +2047,35 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G41" s="3">
         <v>6400</v>
       </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3">
         <v>100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="J41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1827,22 +2088,31 @@
       <c r="N41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E42" s="3">
         <v>10000</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
+      <c r="G42" s="3">
+        <v>10000</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>3</v>
@@ -1853,20 +2123,29 @@
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
+      <c r="K42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1903,8 +2182,17 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1941,28 +2229,37 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>9800</v>
       </c>
       <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
+        <v>14200</v>
+      </c>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3">
         <v>19000</v>
       </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="I45" s="3">
+        <v>0</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -1973,38 +2270,47 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E46" s="3">
+        <v>11600</v>
+      </c>
+      <c r="F46" s="3">
+        <v>14200</v>
+      </c>
+      <c r="G46" s="3">
         <v>16400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>19000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>300</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2017,8 +2323,17 @@
       <c r="N46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2055,32 +2370,41 @@
       <c r="N47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
+        <v>900</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3">
         <v>1500</v>
       </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>100</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2093,8 +2417,17 @@
       <c r="N48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2131,8 +2464,17 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2169,8 +2511,17 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2207,32 +2558,41 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>600</v>
+      </c>
+      <c r="E52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G52" s="3">
+        <v>100</v>
+      </c>
+      <c r="H52" s="3">
         <v>2100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>200</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2245,8 +2605,17 @@
       <c r="N52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2283,32 +2652,41 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>12600</v>
+      </c>
+      <c r="F54" s="3">
+        <v>15500</v>
+      </c>
+      <c r="G54" s="3">
         <v>18000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>21100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>600</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2321,8 +2699,17 @@
       <c r="N54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2337,8 +2724,11 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2353,8 +2743,11 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2391,32 +2784,41 @@
       <c r="N57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3">
+        <v>0</v>
+      </c>
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F58" s="3">
+      <c r="F58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3">
         <v>400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="J58" s="3">
         <v>3500</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2429,31 +2831,40 @@
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3">
         <v>600</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F59" s="3">
+      <c r="F59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G59" s="3">
+        <v>600</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3">
         <v>3900</v>
       </c>
-      <c r="G59" s="3">
-        <v>0</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2467,32 +2878,41 @@
       <c r="N59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3">
         <v>600</v>
       </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F60" s="3">
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3">
+        <v>600</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3">
         <v>4300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2505,8 +2925,17 @@
       <c r="N60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2543,46 +2972,64 @@
       <c r="N61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
+        <v>900</v>
+      </c>
+      <c r="G62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>1400</v>
       </c>
-      <c r="F62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
-      <c r="M62" s="3">
-        <v>0</v>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3">
+        <v>0</v>
+      </c>
+      <c r="P62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2619,8 +3066,17 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2657,8 +3113,17 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2695,32 +3160,41 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>600</v>
+      </c>
+      <c r="F66" s="3">
+        <v>900</v>
+      </c>
+      <c r="G66" s="3">
         <v>1000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>1400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>4300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>3600</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2733,8 +3207,17 @@
       <c r="N66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2749,8 +3232,11 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2787,8 +3273,17 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2825,8 +3320,17 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2863,8 +3367,17 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2901,32 +3414,41 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3">
         <v>-11400</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
         <v>-4000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="J72" s="3">
         <v>-3000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2939,8 +3461,17 @@
       <c r="N72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2977,8 +3508,17 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3015,8 +3555,17 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3053,32 +3602,41 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>14700</v>
+      </c>
+      <c r="G76" s="3">
         <v>17100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>19700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>-4000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>-3000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3091,8 +3649,17 @@
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3129,89 +3696,116 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="F80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="F81" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="G81" s="3">
         <v>-3900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>-3600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>-1300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>-300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
         <v>-800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3226,16 +3820,19 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3">
+        <v>0</v>
       </c>
       <c r="F83" s="3">
         <v>0</v>
@@ -3243,14 +3840,14 @@
       <c r="G83" s="3">
         <v>0</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
@@ -3264,8 +3861,17 @@
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3302,8 +3908,17 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3340,8 +3955,17 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3378,8 +4002,17 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3416,8 +4049,17 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3454,31 +4096,40 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3">
+        <v>0</v>
       </c>
       <c r="F89" s="3">
-        <v>-800</v>
+        <v>0</v>
       </c>
       <c r="G89" s="3">
-        <v>-400</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3492,8 +4143,17 @@
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3508,8 +4168,11 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3534,20 +4197,29 @@
       <c r="J91" s="3">
         <v>0</v>
       </c>
-      <c r="K91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="K91" s="3">
+        <v>0</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3584,8 +4256,17 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3622,16 +4303,25 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
       </c>
       <c r="F94" s="3">
         <v>0</v>
@@ -3639,14 +4329,14 @@
       <c r="G94" s="3">
         <v>0</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>0</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
+      </c>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3660,8 +4350,17 @@
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3676,8 +4375,11 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3714,8 +4416,17 @@
       <c r="N96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3752,8 +4463,17 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3790,8 +4510,17 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3828,31 +4557,40 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
       </c>
       <c r="F100" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G100" s="3">
-        <v>300</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>0</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3866,8 +4604,17 @@
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3904,31 +4651,40 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
+        <v>0</v>
       </c>
       <c r="F102" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
@@ -3940,6 +4696,15 @@
         <v>3</v>
       </c>
       <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="92">
   <si>
     <t>RGC</t>
   </si>
@@ -656,72 +656,73 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -731,31 +732,37 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>0</v>
@@ -778,8 +785,14 @@
       <c r="Q8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3">
+        <v>0</v>
+      </c>
+      <c r="S8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +838,14 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +891,14 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,44 +916,46 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E12" s="3">
         <v>200</v>
       </c>
       <c r="F12" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="G12" s="3">
-        <v>1400</v>
+        <v>200</v>
       </c>
       <c r="H12" s="3">
-        <v>1100</v>
+        <v>100</v>
       </c>
       <c r="I12" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J12" s="3">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="K12" s="3">
         <v>400</v>
       </c>
       <c r="L12" s="3">
+        <v>300</v>
+      </c>
+      <c r="M12" s="3">
+        <v>400</v>
+      </c>
+      <c r="N12" s="3">
         <v>200</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
@@ -938,8 +965,14 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,31 +1018,37 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+        <v>-200</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>-100</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1032,25 +1071,31 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
         <v>0</v>
@@ -1079,8 +1124,14 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,44 +1146,46 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2300</v>
+        <v>1200</v>
       </c>
       <c r="E17" s="3">
-        <v>2800</v>
+        <v>1200</v>
       </c>
       <c r="F17" s="3">
-        <v>3400</v>
+        <v>1200</v>
       </c>
       <c r="G17" s="3">
-        <v>4000</v>
+        <v>1200</v>
       </c>
       <c r="H17" s="3">
-        <v>3700</v>
+        <v>1400</v>
       </c>
       <c r="I17" s="3">
         <v>1400</v>
       </c>
       <c r="J17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L17" s="3">
         <v>400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1142,44 +1195,50 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-1200</v>
       </c>
       <c r="E18" s="3">
-        <v>-2800</v>
+        <v>-1200</v>
       </c>
       <c r="F18" s="3">
-        <v>-3400</v>
+        <v>-1200</v>
       </c>
       <c r="G18" s="3">
-        <v>-4000</v>
+        <v>-1200</v>
       </c>
       <c r="H18" s="3">
-        <v>-3700</v>
+        <v>-1400</v>
       </c>
       <c r="I18" s="3">
         <v>-1400</v>
       </c>
       <c r="J18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="L18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>-300</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1189,8 +1248,14 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,31 +1273,33 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H20" s="3">
         <v>100</v>
       </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1240,11 +1307,11 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1255,43 +1322,49 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="F21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-1400</v>
       </c>
       <c r="I21" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K21" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K21" s="3">
-        <v>-800</v>
       </c>
       <c r="L21" s="3">
         <v>-300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
+      <c r="M21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N21" s="3">
+        <v>-300</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
@@ -1302,31 +1375,37 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1349,43 +1428,49 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-2200</v>
+        <v>-1100</v>
       </c>
       <c r="E23" s="3">
-        <v>-2700</v>
+        <v>-1100</v>
       </c>
       <c r="F23" s="3">
-        <v>-3300</v>
+        <v>-1100</v>
       </c>
       <c r="G23" s="3">
-        <v>-3900</v>
+        <v>-1100</v>
       </c>
       <c r="H23" s="3">
-        <v>-3700</v>
+        <v>-1400</v>
       </c>
       <c r="I23" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J23" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K23" s="3">
-        <v>-800</v>
       </c>
       <c r="L23" s="3">
         <v>-300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
+      <c r="M23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N23" s="3">
+        <v>-300</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
@@ -1396,31 +1481,37 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1443,8 +1534,14 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,43 +1587,49 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-2200</v>
+        <v>-1100</v>
       </c>
       <c r="E26" s="3">
-        <v>-2700</v>
+        <v>-1100</v>
       </c>
       <c r="F26" s="3">
-        <v>-3300</v>
+        <v>-1100</v>
       </c>
       <c r="G26" s="3">
-        <v>-3900</v>
+        <v>-1100</v>
       </c>
       <c r="H26" s="3">
-        <v>-3700</v>
+        <v>-1400</v>
       </c>
       <c r="I26" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="K26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="K26" s="3">
-        <v>-800</v>
       </c>
       <c r="L26" s="3">
         <v>-300</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
+      <c r="M26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-300</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
@@ -1537,43 +1640,49 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-2100</v>
+        <v>-1100</v>
       </c>
       <c r="E27" s="3">
-        <v>-2600</v>
+        <v>-1100</v>
       </c>
       <c r="F27" s="3">
-        <v>-3200</v>
+        <v>-1000</v>
       </c>
       <c r="G27" s="3">
-        <v>-3900</v>
+        <v>-1000</v>
       </c>
       <c r="H27" s="3">
-        <v>-3600</v>
+        <v>-1300</v>
       </c>
       <c r="I27" s="3">
         <v>-1300</v>
       </c>
       <c r="J27" s="3">
-        <v>-300</v>
+        <v>-1600</v>
       </c>
       <c r="K27" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="L27" s="3">
         <v>-300</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
+      <c r="M27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N27" s="3">
+        <v>-300</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
@@ -1584,8 +1693,14 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1746,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1799,14 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1852,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,31 +1905,37 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
         <v>-100</v>
       </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1804,11 +1943,11 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1819,43 +1958,49 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-2100</v>
+        <v>-1100</v>
       </c>
       <c r="E33" s="3">
-        <v>-2600</v>
+        <v>-1100</v>
       </c>
       <c r="F33" s="3">
-        <v>-3200</v>
+        <v>-1000</v>
       </c>
       <c r="G33" s="3">
-        <v>-3900</v>
+        <v>-1000</v>
       </c>
       <c r="H33" s="3">
-        <v>-3600</v>
+        <v>-1300</v>
       </c>
       <c r="I33" s="3">
         <v>-1300</v>
       </c>
       <c r="J33" s="3">
-        <v>-300</v>
+        <v>-1600</v>
       </c>
       <c r="K33" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="L33" s="3">
         <v>-300</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
+      <c r="M33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N33" s="3">
+        <v>-300</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
@@ -1866,8 +2011,14 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,43 +2064,49 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-2100</v>
+        <v>-1100</v>
       </c>
       <c r="E35" s="3">
-        <v>-2600</v>
+        <v>-1100</v>
       </c>
       <c r="F35" s="3">
-        <v>-3200</v>
+        <v>-1000</v>
       </c>
       <c r="G35" s="3">
-        <v>-3900</v>
+        <v>-1000</v>
       </c>
       <c r="H35" s="3">
-        <v>-3600</v>
+        <v>-1300</v>
       </c>
       <c r="I35" s="3">
         <v>-1300</v>
       </c>
       <c r="J35" s="3">
-        <v>-300</v>
+        <v>-1600</v>
       </c>
       <c r="K35" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="L35" s="3">
         <v>-300</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
+      <c r="M35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N35" s="3">
+        <v>-300</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
@@ -1960,49 +2117,55 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2012,8 +2175,14 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2200,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,38 +2221,40 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>3</v>
+      <c r="D41" s="3">
+        <v>3000</v>
       </c>
       <c r="E41" s="3">
+        <v>3000</v>
+      </c>
+      <c r="F41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H41" s="3">
         <v>1600</v>
       </c>
-      <c r="F41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G41" s="3">
-        <v>6400</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3">
+        <v>1600</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2097,31 +2270,37 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>3</v>
+      <c r="D42" s="3">
+        <v>5000</v>
       </c>
       <c r="E42" s="3">
+        <v>5000</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>10000</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>10000</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2132,11 +2311,11 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2144,31 +2323,37 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>0</v>
-      </c>
-      <c r="G43" s="3">
-        <v>0</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2191,31 +2376,37 @@
       <c r="Q43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+      <c r="S43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2238,34 +2429,40 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>9800</v>
-      </c>
-      <c r="E45" s="3">
-        <v>100</v>
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>5000</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
         <v>14200</v>
       </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>19000</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
+      <c r="K45" s="3">
+        <v>0</v>
       </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
@@ -2279,44 +2476,50 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+      <c r="S45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F46" s="3">
         <v>9800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
+        <v>9800</v>
+      </c>
+      <c r="H46" s="3">
         <v>11600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
+        <v>11600</v>
+      </c>
+      <c r="J46" s="3">
         <v>14200</v>
       </c>
-      <c r="G46" s="3">
-        <v>16400</v>
-      </c>
-      <c r="H46" s="3">
-        <v>19000</v>
-      </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>300</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2332,31 +2535,37 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -2379,38 +2588,44 @@
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>200</v>
       </c>
       <c r="E48" s="3">
+        <v>200</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3">
+        <v>900</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3">
         <v>100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>100</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2426,8 +2641,14 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2473,8 +2694,14 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2747,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,38 +2800,44 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>100</v>
       </c>
       <c r="F52" s="3">
+        <v>600</v>
+      </c>
+      <c r="G52" s="3">
+        <v>600</v>
+      </c>
+      <c r="H52" s="3">
+        <v>100</v>
+      </c>
+      <c r="I52" s="3">
+        <v>100</v>
+      </c>
+      <c r="J52" s="3">
         <v>1400</v>
       </c>
-      <c r="G52" s="3">
-        <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>200</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2614,8 +2853,14 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,38 +2906,44 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F54" s="3">
         <v>10500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
+        <v>10500</v>
+      </c>
+      <c r="H54" s="3">
         <v>12600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
+        <v>12600</v>
+      </c>
+      <c r="J54" s="3">
         <v>15500</v>
       </c>
-      <c r="G54" s="3">
-        <v>18000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>21100</v>
-      </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2708,8 +2959,14 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2984,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,31 +3005,33 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2793,38 +3054,44 @@
       <c r="Q57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3">
+        <v>0</v>
+      </c>
+      <c r="S57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>100</v>
+      </c>
+      <c r="F58" s="3">
+        <v>0</v>
       </c>
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>400</v>
       </c>
       <c r="I58" s="3">
         <v>400</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>400</v>
+      </c>
+      <c r="L58" s="3">
         <v>3500</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2840,37 +3107,43 @@
       <c r="Q58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G59" s="3">
-        <v>600</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
+      <c r="G59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
       </c>
       <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>3900</v>
       </c>
-      <c r="J59" s="3">
-        <v>0</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
+      <c r="L59" s="3">
+        <v>0</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
@@ -2887,38 +3160,44 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>200</v>
       </c>
       <c r="E60" s="3">
+        <v>200</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
         <v>600</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>600</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>4300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2934,8 +3213,14 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2981,32 +3266,38 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3">
         <v>300</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
-      </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
+        <v>300</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>900</v>
       </c>
-      <c r="G62" s="3">
-        <v>400</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3016,11 +3307,11 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
-      </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3028,8 +3319,14 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3372,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3425,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,38 +3478,44 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>200</v>
+      </c>
+      <c r="F66" s="3">
         <v>300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
+        <v>300</v>
+      </c>
+      <c r="H66" s="3">
         <v>600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
+        <v>600</v>
+      </c>
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="G66" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H66" s="3">
-        <v>1400</v>
-      </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>4300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3600</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3216,8 +3531,14 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3556,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3605,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3658,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3711,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,38 +3764,44 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-21600</v>
       </c>
       <c r="E72" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3">
         <v>-17300</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3">
+        <v>-17300</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>-4000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-3000</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3817,14 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3870,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3923,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,38 +3976,44 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F76" s="3">
         <v>10200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
+        <v>10200</v>
+      </c>
+      <c r="H76" s="3">
         <v>12000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J76" s="3">
         <v>14700</v>
       </c>
-      <c r="G76" s="3">
-        <v>17100</v>
-      </c>
-      <c r="H76" s="3">
-        <v>19700</v>
-      </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-4000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-3000</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3658,8 +4029,14 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,49 +4082,55 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3757,43 +4140,49 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-2100</v>
+        <v>-1100</v>
       </c>
       <c r="E81" s="3">
-        <v>-2600</v>
+        <v>-1100</v>
       </c>
       <c r="F81" s="3">
-        <v>-3200</v>
+        <v>-1000</v>
       </c>
       <c r="G81" s="3">
-        <v>-3900</v>
+        <v>-1000</v>
       </c>
       <c r="H81" s="3">
-        <v>-3600</v>
+        <v>-1300</v>
       </c>
       <c r="I81" s="3">
         <v>-1300</v>
       </c>
       <c r="J81" s="3">
-        <v>-300</v>
+        <v>-1600</v>
       </c>
       <c r="K81" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="L81" s="3">
         <v>-300</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
+      <c r="M81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="N81" s="3">
+        <v>-300</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
@@ -3804,8 +4193,14 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,37 +4218,39 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
-      </c>
-      <c r="F83" s="3">
-        <v>0</v>
-      </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3">
+        <v>0</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3870,8 +4267,14 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4320,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4373,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4426,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4479,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,37 +4532,43 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>0</v>
-      </c>
-      <c r="E89" s="3">
-        <v>0</v>
-      </c>
-      <c r="F89" s="3">
-        <v>0</v>
-      </c>
-      <c r="G89" s="3">
-        <v>0</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3">
-        <v>0</v>
-      </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
+        <v>0</v>
       </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
@@ -4152,8 +4585,14 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,31 +4610,33 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4206,11 +4647,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4218,8 +4659,14 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4712,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,37 +4765,43 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>0</v>
-      </c>
-      <c r="E94" s="3">
-        <v>0</v>
-      </c>
-      <c r="F94" s="3">
-        <v>0</v>
-      </c>
-      <c r="G94" s="3">
-        <v>0</v>
-      </c>
-      <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K94" s="3">
+        <v>0</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -4359,8 +4818,14 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,31 +4843,33 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4425,8 +4892,14 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4945,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4998,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,37 +5051,43 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>0</v>
-      </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
-      <c r="F100" s="3">
-        <v>0</v>
-      </c>
-      <c r="G100" s="3">
-        <v>0</v>
-      </c>
-      <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K100" s="3">
+        <v>0</v>
+      </c>
+      <c r="L100" s="3">
+        <v>0</v>
       </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
@@ -4613,31 +5104,37 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -4660,8 +5157,14 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -4686,11 +5189,11 @@
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
@@ -4705,6 +5208,12 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="92">
   <si>
     <t>RGC</t>
   </si>
@@ -656,79 +656,80 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44196</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44012</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43830</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
@@ -738,8 +739,14 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -764,11 +771,11 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -791,8 +798,14 @@
       <c r="S8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3">
+        <v>0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -844,8 +857,14 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -897,8 +916,14 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,16 +943,18 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3">
-        <v>200</v>
-      </c>
-      <c r="E12" s="3">
-        <v>200</v>
+      <c r="D12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
@@ -935,33 +962,33 @@
       <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>700</v>
-      </c>
-      <c r="K12" s="3">
-        <v>400</v>
-      </c>
-      <c r="L12" s="3">
-        <v>300</v>
       </c>
       <c r="M12" s="3">
         <v>400</v>
       </c>
       <c r="N12" s="3">
+        <v>300</v>
+      </c>
+      <c r="O12" s="3">
+        <v>400</v>
+      </c>
+      <c r="P12" s="3">
         <v>200</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -971,8 +998,14 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1024,37 +1057,43 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>-200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-200</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1077,16 +1116,22 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
         <v>100</v>
@@ -1095,14 +1140,14 @@
         <v>100</v>
       </c>
       <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
         <v>100</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
@@ -1130,8 +1175,14 @@
       <c r="S15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1148,16 +1199,18 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>1200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>1200</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F17" s="3">
         <v>1200</v>
@@ -1165,33 +1218,33 @@
       <c r="G17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J17" s="3">
         <v>1400</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1400</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1700</v>
       </c>
       <c r="K17" s="3">
         <v>1400</v>
       </c>
       <c r="L17" s="3">
+        <v>1700</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1400</v>
+      </c>
+      <c r="N17" s="3">
         <v>400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1201,16 +1254,22 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-1200</v>
-      </c>
-      <c r="E18" s="3">
-        <v>-1200</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F18" s="3">
         <v>-1200</v>
@@ -1218,33 +1277,33 @@
       <c r="G18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1400</v>
-      </c>
-      <c r="I18" s="3">
-        <v>-1400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>-1700</v>
       </c>
       <c r="K18" s="3">
         <v>-1400</v>
       </c>
       <c r="L18" s="3">
+        <v>-1700</v>
+      </c>
+      <c r="M18" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="N18" s="3">
         <v>-400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-300</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1254,8 +1313,14 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1275,49 +1340,51 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
+        <v>100</v>
+      </c>
+      <c r="K20" s="3">
+        <v>100</v>
+      </c>
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>100</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1328,49 +1395,55 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>-1200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-1200</v>
       </c>
-      <c r="F21" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>-1000</v>
-      </c>
       <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-1400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-1600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L21" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M21" s="3">
-        <v>-800</v>
       </c>
       <c r="N21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
+      <c r="O21" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P21" s="3">
+        <v>-300</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
@@ -1381,8 +1454,14 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1407,11 +1486,11 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1434,16 +1513,22 @@
       <c r="S22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-1100</v>
+      <c r="D23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F23" s="3">
         <v>-1100</v>
@@ -1451,32 +1536,32 @@
       <c r="G23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-1400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L23" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M23" s="3">
-        <v>-800</v>
       </c>
       <c r="N23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
+      <c r="O23" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P23" s="3">
+        <v>-300</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
@@ -1487,8 +1572,14 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1513,11 +1604,11 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1540,8 +1631,14 @@
       <c r="S24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1593,16 +1690,22 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>-1100</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F26" s="3">
         <v>-1100</v>
@@ -1610,32 +1713,32 @@
       <c r="G26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-1400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-1700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-1300</v>
-      </c>
-      <c r="L26" s="3">
-        <v>-300</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-800</v>
       </c>
       <c r="N26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
+      <c r="O26" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P26" s="3">
+        <v>-300</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
@@ -1646,49 +1749,55 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F27" s="3">
         <v>-1100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-1100</v>
       </c>
-      <c r="F27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H27" s="3">
+      <c r="H27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I27" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J27" s="3">
-        <v>-1600</v>
       </c>
       <c r="K27" s="3">
         <v>-1300</v>
       </c>
       <c r="L27" s="3">
-        <v>-300</v>
+        <v>-1600</v>
       </c>
       <c r="M27" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="N27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
+      <c r="O27" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P27" s="3">
+        <v>-300</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
@@ -1699,8 +1808,14 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1752,8 +1867,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1805,8 +1926,14 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1858,8 +1985,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1911,49 +2044,55 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="G32" s="3">
-        <v>100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="J32" s="3">
-        <v>100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1964,49 +2103,55 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F33" s="3">
         <v>-1100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-1100</v>
       </c>
-      <c r="F33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H33" s="3">
+      <c r="H33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J33" s="3">
-        <v>-1600</v>
       </c>
       <c r="K33" s="3">
         <v>-1300</v>
       </c>
       <c r="L33" s="3">
-        <v>-300</v>
+        <v>-1600</v>
       </c>
       <c r="M33" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="N33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
+      <c r="O33" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P33" s="3">
+        <v>-300</v>
       </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
@@ -2017,8 +2162,14 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2070,49 +2221,55 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F35" s="3">
         <v>-1100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-1100</v>
       </c>
-      <c r="F35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="H35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I35" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J35" s="3">
-        <v>-1600</v>
       </c>
       <c r="K35" s="3">
         <v>-1300</v>
       </c>
       <c r="L35" s="3">
-        <v>-300</v>
+        <v>-1600</v>
       </c>
       <c r="M35" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="N35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
+      <c r="O35" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P35" s="3">
+        <v>-300</v>
       </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
@@ -2123,55 +2280,61 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44196</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44012</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43830</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2181,8 +2344,14 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2202,8 +2371,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2223,44 +2394,46 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3">
         <v>3000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3000</v>
       </c>
-      <c r="F41" s="3">
-        <v>4800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>4800</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>1600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1600</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3">
         <v>100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>300</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2276,37 +2449,43 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>5000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>5000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>10000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>10000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
+      <c r="L42" s="3">
+        <v>0</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
@@ -2317,11 +2496,11 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
@@ -2329,8 +2508,14 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2355,11 +2540,11 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
@@ -2382,8 +2567,14 @@
       <c r="S43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2408,11 +2599,11 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2435,8 +2626,14 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2446,11 +2643,11 @@
       <c r="E45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F45" s="3">
-        <v>5000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>5000</v>
+      <c r="F45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -2458,17 +2655,17 @@
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>14200</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
+      <c r="M45" s="3">
+        <v>0</v>
       </c>
       <c r="N45" s="3" t="s">
         <v>3</v>
@@ -2482,50 +2679,56 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3">
+        <v>0</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F46" s="3">
         <v>8100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>8100</v>
       </c>
-      <c r="F46" s="3">
-        <v>9800</v>
-      </c>
-      <c r="G46" s="3">
-        <v>9800</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J46" s="3">
         <v>11600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>300</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2541,8 +2744,14 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2567,11 +2776,11 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -2594,44 +2803,50 @@
       <c r="S47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3">
+        <v>0</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>200</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>900</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>100</v>
       </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2647,16 +2862,22 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
-        <v>0</v>
-      </c>
-      <c r="E49" s="3">
-        <v>0</v>
+      <c r="D49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2664,11 +2885,11 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
+      <c r="H49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -2700,8 +2921,14 @@
       <c r="S49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3">
+        <v>0</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2753,8 +2980,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2806,44 +3039,50 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
-        <v>600</v>
-      </c>
-      <c r="G52" s="3">
-        <v>600</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="H52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>200</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2859,8 +3098,14 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2912,44 +3157,50 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="3">
         <v>8400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8400</v>
       </c>
-      <c r="F54" s="3">
-        <v>10500</v>
-      </c>
-      <c r="G54" s="3">
-        <v>10500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J54" s="3">
         <v>12600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>12600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>15500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>600</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,8 +3216,14 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2986,8 +3243,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3007,8 +3266,10 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3033,11 +3294,11 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
@@ -3060,44 +3321,50 @@
       <c r="S57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3">
+        <v>0</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="3">
         <v>100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J58" s="3">
         <v>400</v>
-      </c>
-      <c r="I58" s="3">
-        <v>400</v>
-      </c>
-      <c r="J58" s="3">
-        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>400</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>400</v>
+      </c>
+      <c r="N58" s="3">
         <v>3500</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3113,43 +3380,49 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
-        <v>0</v>
-      </c>
-      <c r="I59" s="3">
-        <v>0</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
       </c>
       <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3">
         <v>3900</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
+      <c r="N59" s="3">
+        <v>0</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
@@ -3166,44 +3439,50 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F60" s="3">
         <v>200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>200</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
         <v>600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>600</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3">
         <v>4300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3219,8 +3498,14 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3272,8 +3557,14 @@
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3283,11 +3574,11 @@
       <c r="E62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F62" s="3">
-        <v>300</v>
-      </c>
-      <c r="G62" s="3">
-        <v>300</v>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -3295,15 +3586,15 @@
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>900</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3313,11 +3604,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
@@ -3325,8 +3616,14 @@
       <c r="S62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3378,8 +3675,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3431,8 +3734,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3484,44 +3793,50 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="3">
         <v>200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>200</v>
       </c>
-      <c r="F66" s="3">
-        <v>300</v>
-      </c>
-      <c r="G66" s="3">
-        <v>300</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J66" s="3">
         <v>600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3600</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3537,8 +3852,14 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3558,8 +3879,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3611,8 +3934,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3664,8 +3993,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3717,8 +4052,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3770,44 +4111,50 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
         <v>-21600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-21600</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-17300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-17300</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3">
         <v>-4000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-3000</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3823,8 +4170,14 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3876,8 +4229,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3929,8 +4288,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3982,44 +4347,50 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="3">
         <v>8200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8200</v>
       </c>
-      <c r="F76" s="3">
-        <v>10200</v>
-      </c>
-      <c r="G76" s="3">
-        <v>10200</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J76" s="3">
         <v>12000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>12000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>14700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-4000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-3000</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4035,8 +4406,14 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4088,55 +4465,61 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44196</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44012</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43830</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4146,49 +4529,55 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F81" s="3">
         <v>-1100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-1100</v>
       </c>
-      <c r="F81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="H81" s="3">
+      <c r="H81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1300</v>
-      </c>
-      <c r="I81" s="3">
-        <v>-1300</v>
-      </c>
-      <c r="J81" s="3">
-        <v>-1600</v>
       </c>
       <c r="K81" s="3">
         <v>-1300</v>
       </c>
       <c r="L81" s="3">
-        <v>-300</v>
+        <v>-1600</v>
       </c>
       <c r="M81" s="3">
-        <v>-800</v>
+        <v>-1300</v>
       </c>
       <c r="N81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
+      <c r="O81" s="3">
+        <v>-800</v>
+      </c>
+      <c r="P81" s="3">
+        <v>-300</v>
       </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
@@ -4199,8 +4588,14 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4220,8 +4615,10 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4246,17 +4643,17 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -4273,8 +4670,14 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4326,8 +4729,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4379,8 +4788,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4432,8 +4847,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4485,8 +4906,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4538,8 +4965,14 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -4564,17 +4997,17 @@
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
-        <v>0</v>
-      </c>
-      <c r="L89" s="3">
-        <v>0</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
+        <v>0</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -4591,8 +5024,14 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4612,8 +5051,10 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4638,11 +5079,11 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -4653,11 +5094,11 @@
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -4665,8 +5106,14 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4718,8 +5165,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4771,8 +5224,14 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -4797,17 +5256,17 @@
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
+      </c>
+      <c r="N94" s="3">
+        <v>0</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -4824,8 +5283,14 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4845,8 +5310,10 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4871,11 +5338,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4898,8 +5365,14 @@
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4951,8 +5424,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5004,8 +5483,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5057,8 +5542,14 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5083,17 +5574,17 @@
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
-        <v>0</v>
-      </c>
-      <c r="L100" s="3">
-        <v>0</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
+        <v>0</v>
+      </c>
+      <c r="N100" s="3">
+        <v>0</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -5110,8 +5601,14 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5136,11 +5633,11 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -5163,8 +5660,14 @@
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5195,11 +5698,11 @@
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
+        <v>0</v>
       </c>
       <c r="O102" s="3" t="s">
         <v>3</v>
@@ -5214,6 +5717,12 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RGC_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="92">
   <si>
     <t>RGC</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
@@ -668,85 +668,100 @@
     <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="21" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="P7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -777,17 +792,17 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0</v>
-      </c>
-      <c r="O8" s="3">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0</v>
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q8" s="3">
         <v>0</v>
@@ -804,8 +819,20 @@
       <c r="U8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -863,8 +890,20 @@
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -922,8 +961,20 @@
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -945,16 +996,20 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>3</v>
+      <c r="D12" s="3">
+        <v>200</v>
+      </c>
+      <c r="E12" s="3">
+        <v>200</v>
       </c>
       <c r="F12" s="3">
         <v>200</v>
@@ -962,50 +1017,62 @@
       <c r="G12" s="3">
         <v>200</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
+      <c r="H12" s="3">
+        <v>300</v>
+      </c>
+      <c r="I12" s="3">
+        <v>300</v>
       </c>
       <c r="J12" s="3">
+        <v>200</v>
+      </c>
+      <c r="K12" s="3">
+        <v>200</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3">
         <v>100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="O12" s="3">
         <v>100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="P12" s="3">
         <v>700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="Q12" s="3">
         <v>400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="R12" s="3">
         <v>300</v>
       </c>
-      <c r="O12" s="3">
+      <c r="S12" s="3">
         <v>400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="T12" s="3">
         <v>200</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1063,8 +1130,20 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1075,37 +1154,37 @@
         <v>3</v>
       </c>
       <c r="F14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G14" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3">
         <v>-200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="K14" s="3">
         <v>-200</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
+      <c r="O14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1122,8 +1201,20 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1134,22 +1225,22 @@
         <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>100</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1158,7 +1249,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1181,8 +1272,20 @@
       <c r="U15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1201,126 +1304,154 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+      <c r="W16" s="3"/>
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2700</v>
       </c>
       <c r="F17" s="3">
+        <v>900</v>
+      </c>
+      <c r="G17" s="3">
+        <v>900</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J17" s="3">
         <v>1200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3">
         <v>1400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="O17" s="3">
         <v>1400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="P17" s="3">
         <v>1700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <v>1400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <v>400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <v>800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-2700</v>
       </c>
       <c r="F18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J18" s="3">
         <v>-1200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="K18" s="3">
         <v>-1200</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3">
         <v>-1400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="P18" s="3">
         <v>-1700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>-400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>-800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>-300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,16 +1473,20 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
       </c>
       <c r="F20" s="3">
         <v>100</v>
@@ -1359,11 +1494,11 @@
       <c r="G20" s="3">
         <v>100</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>-100</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>100</v>
@@ -1371,97 +1506,121 @@
       <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3">
+        <v>100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>100</v>
+      </c>
+      <c r="P20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
       </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="E21" s="3">
-        <v>0</v>
+        <v>-2600</v>
       </c>
       <c r="F21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I21" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J21" s="3">
         <v>-1200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="K21" s="3">
         <v>-1200</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3">
         <v>-1400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="O21" s="3">
         <v>-1400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="P21" s="3">
         <v>-1600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="Q21" s="3">
         <v>-1300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="R21" s="3">
         <v>-300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="S21" s="3">
         <v>-800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="T21" s="3">
         <v>-300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1492,17 +1651,17 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1519,67 +1678,91 @@
       <c r="U22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>3</v>
+      <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-2700</v>
       </c>
       <c r="F23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J23" s="3">
         <v>-1100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="K23" s="3">
         <v>-1100</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3">
         <v>-1400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="O23" s="3">
         <v>-1400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="P23" s="3">
         <v>-1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="Q23" s="3">
         <v>-1300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="S23" s="3">
         <v>-800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1610,17 +1793,17 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
-      <c r="P24" s="3">
-        <v>0</v>
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q24" s="3">
         <v>0</v>
@@ -1637,8 +1820,20 @@
       <c r="U24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1696,126 +1891,162 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-2700</v>
       </c>
       <c r="F26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J26" s="3">
         <v>-1100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="K26" s="3">
         <v>-1100</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3">
         <v>-1400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="O26" s="3">
         <v>-1400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="P26" s="3">
         <v>-1700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="Q26" s="3">
         <v>-1300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="R26" s="3">
         <v>-300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="S26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="T26" s="3">
         <v>-300</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-2700</v>
       </c>
       <c r="F27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J27" s="3">
         <v>-1100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="K27" s="3">
         <v>-1100</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="O27" s="3">
         <v>-1300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="P27" s="3">
         <v>-1600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="Q27" s="3">
         <v>-1300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="S27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1873,8 +2104,20 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1932,8 +2175,20 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1991,8 +2246,20 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2050,16 +2317,28 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
       </c>
       <c r="F32" s="3">
         <v>-100</v>
@@ -2067,11 +2346,11 @@
       <c r="G32" s="3">
         <v>-100</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>100</v>
+      </c>
+      <c r="I32" s="3">
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>-100</v>
@@ -2079,97 +2358,121 @@
       <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="P32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
       </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-2700</v>
       </c>
       <c r="F33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J33" s="3">
         <v>-1100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="K33" s="3">
         <v>-1100</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="O33" s="3">
         <v>-1300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="P33" s="3">
         <v>-1600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>-1300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>-300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>-300</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2227,131 +2530,167 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-2700</v>
       </c>
       <c r="F35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J35" s="3">
         <v>-1100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="K35" s="3">
         <v>-1100</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="O35" s="3">
         <v>-1300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="P35" s="3">
         <v>-1600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="Q35" s="3">
         <v>-1300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="R35" s="3">
         <v>-300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="T35" s="3">
         <v>-300</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="P38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2373,8 +2712,12 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+      <c r="W39" s="3"/>
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2396,56 +2739,60 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+      <c r="W40" s="3"/>
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>3</v>
+      <c r="D41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2400</v>
       </c>
       <c r="F41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="G41" s="3">
+        <v>2400</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J41" s="3">
         <v>3000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>3000</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3">
         <v>1600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>1600</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3">
         <v>100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2455,8 +2802,20 @@
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2467,55 +2826,67 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G42" s="3">
+        <v>2500</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>5000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="K42" s="3">
         <v>5000</v>
       </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>10000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>10000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
+      <c r="P42" s="3">
+        <v>0</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2546,17 +2917,17 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3">
-        <v>0</v>
-      </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q43" s="3">
         <v>0</v>
@@ -2573,8 +2944,20 @@
       <c r="U43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+      <c r="W43" s="3">
+        <v>0</v>
+      </c>
+      <c r="X43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2605,17 +2988,17 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2632,8 +3015,20 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2649,11 +3044,11 @@
       <c r="G45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
+      <c r="H45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>6600</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
@@ -2661,23 +3056,23 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P45" s="3">
         <v>14200</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
+      <c r="Q45" s="3">
+        <v>0</v>
       </c>
       <c r="R45" s="3" t="s">
         <v>3</v>
@@ -2685,62 +3080,74 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T45" s="3">
-        <v>0</v>
-      </c>
-      <c r="U45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>3</v>
+      <c r="D46" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2400</v>
       </c>
       <c r="F46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G46" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H46" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I46" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J46" s="3">
         <v>8100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>8100</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3">
         <v>11600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>11600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>14200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>300</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2750,8 +3157,20 @@
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2782,17 +3201,17 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -2809,56 +3228,68 @@
       <c r="U47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V47" s="3">
+        <v>0</v>
+      </c>
+      <c r="W47" s="3">
+        <v>0</v>
+      </c>
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>600</v>
       </c>
       <c r="F48" s="3">
+        <v>800</v>
+      </c>
+      <c r="G48" s="3">
+        <v>800</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>200</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
         <v>900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>100</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2868,16 +3299,28 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>3</v>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -2885,11 +3328,11 @@
       <c r="G49" s="3">
         <v>0</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
+      <c r="H49" s="3">
+        <v>0</v>
+      </c>
+      <c r="I49" s="3">
+        <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
@@ -2897,11 +3340,11 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3">
-        <v>0</v>
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N49" s="3">
         <v>0</v>
@@ -2927,8 +3370,20 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2986,8 +3441,20 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3045,16 +3512,28 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="D52" s="3">
+        <v>100</v>
+      </c>
+      <c r="E52" s="3">
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>100</v>
@@ -3062,11 +3541,11 @@
       <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
+      <c r="H52" s="3">
+        <v>900</v>
+      </c>
+      <c r="I52" s="3">
+        <v>900</v>
       </c>
       <c r="J52" s="3">
         <v>100</v>
@@ -3074,27 +3553,27 @@
       <c r="K52" s="3">
         <v>100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3">
+        <v>100</v>
+      </c>
+      <c r="O52" s="3">
+        <v>100</v>
+      </c>
+      <c r="P52" s="3">
         <v>1400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>200</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3104,8 +3583,20 @@
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3163,56 +3654,68 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>3</v>
+      <c r="D54" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3000</v>
       </c>
       <c r="F54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="G54" s="3">
+        <v>5800</v>
+      </c>
+      <c r="H54" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I54" s="3">
+        <v>7500</v>
+      </c>
+      <c r="J54" s="3">
         <v>8400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>8400</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3">
         <v>12600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>12600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>15500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3222,8 +3725,20 @@
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3245,8 +3760,12 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+      <c r="W55" s="3"/>
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3268,8 +3787,12 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+      <c r="W56" s="3"/>
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3300,17 +3823,17 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q57" s="3">
         <v>0</v>
@@ -3327,56 +3850,68 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>300</v>
       </c>
       <c r="F58" s="3">
+        <v>300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>100</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3">
         <v>400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>400</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="R58" s="3">
         <v>3500</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3386,16 +3921,28 @@
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>3</v>
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
       </c>
       <c r="F59" s="3">
         <v>0</v>
@@ -3418,23 +3965,23 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3">
+        <v>0</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3">
         <v>3900</v>
       </c>
-      <c r="N59" s="3">
-        <v>0</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3445,56 +3992,68 @@
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>3</v>
+      <c r="D60" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1700</v>
       </c>
       <c r="F60" s="3">
+        <v>700</v>
+      </c>
+      <c r="G60" s="3">
+        <v>700</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
         <v>200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>200</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3">
         <v>600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>600</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3">
         <v>4300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,22 +4063,34 @@
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -3563,8 +4134,20 @@
       <c r="U61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3580,11 +4163,11 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
+      <c r="H62" s="3">
+        <v>800</v>
+      </c>
+      <c r="I62" s="3">
+        <v>800</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
@@ -3592,38 +4175,50 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P62" s="3">
         <v>900</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-      <c r="T62" s="3">
-        <v>0</v>
-      </c>
-      <c r="U62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+      <c r="W62" s="3">
+        <v>0</v>
+      </c>
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3681,8 +4276,20 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3740,8 +4347,20 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3799,56 +4418,68 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>3</v>
+      <c r="D66" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1800</v>
       </c>
       <c r="F66" s="3">
+        <v>900</v>
+      </c>
+      <c r="G66" s="3">
+        <v>900</v>
+      </c>
+      <c r="H66" s="3">
+        <v>800</v>
+      </c>
+      <c r="I66" s="3">
+        <v>800</v>
+      </c>
+      <c r="J66" s="3">
         <v>200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>200</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3">
         <v>600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>4300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>3600</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +4489,20 @@
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3881,8 +4524,12 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+      <c r="W67" s="3"/>
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3940,8 +4587,20 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3999,8 +4658,20 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4058,8 +4729,20 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4117,56 +4800,68 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>3</v>
+      <c r="D72" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-30500</v>
       </c>
       <c r="F72" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-25200</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
         <v>-21600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>-21600</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3">
         <v>-17300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>-17300</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3">
         <v>-4000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>-3000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4871,20 @@
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4235,8 +4942,20 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4294,8 +5013,20 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4353,56 +5084,68 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>3</v>
+      <c r="D76" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1200</v>
       </c>
       <c r="F76" s="3">
+        <v>4900</v>
+      </c>
+      <c r="G76" s="3">
+        <v>4900</v>
+      </c>
+      <c r="H76" s="3">
+        <v>6700</v>
+      </c>
+      <c r="I76" s="3">
+        <v>6700</v>
+      </c>
+      <c r="J76" s="3">
         <v>8200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>8200</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3">
         <v>12000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>12000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>14700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>-4000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>-3000</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4412,8 +5155,20 @@
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4471,131 +5226,167 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="P80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="W80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-2700</v>
       </c>
       <c r="F81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-900</v>
+      </c>
+      <c r="J81" s="3">
         <v>-1100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="K81" s="3">
         <v>-1100</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="O81" s="3">
         <v>-1300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="P81" s="3">
         <v>-1600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="Q81" s="3">
         <v>-1300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="R81" s="3">
         <v>-300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="T81" s="3">
         <v>-300</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4617,8 +5408,12 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+      <c r="W82" s="3"/>
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4649,11 +5444,11 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O83" s="3" t="s">
         <v>3</v>
@@ -4661,11 +5456,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+      <c r="R83" s="3">
+        <v>0</v>
       </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
@@ -4676,8 +5471,20 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4735,8 +5542,20 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4794,8 +5613,20 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4853,8 +5684,20 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4912,8 +5755,20 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4971,16 +5826,28 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1300</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>3</v>
@@ -4988,11 +5855,11 @@
       <c r="G89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+      <c r="H89" s="3">
+        <v>-900</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-900</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
@@ -5003,11 +5870,11 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
-        <v>0</v>
-      </c>
-      <c r="N89" s="3">
-        <v>0</v>
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
@@ -5015,11 +5882,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
+      <c r="Q89" s="3">
+        <v>0</v>
+      </c>
+      <c r="R89" s="3">
+        <v>0</v>
       </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
@@ -5030,8 +5897,20 @@
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5053,8 +5932,12 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5085,35 +5968,47 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3">
-        <v>0</v>
-      </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5171,8 +6066,20 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5230,16 +6137,28 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>1300</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>3</v>
@@ -5247,11 +6166,11 @@
       <c r="G94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>100</v>
+      </c>
+      <c r="I94" s="3">
+        <v>100</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
@@ -5262,11 +6181,11 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
-      </c>
-      <c r="N94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
@@ -5274,11 +6193,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5289,8 +6208,20 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5312,8 +6243,12 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+      <c r="W95" s="3"/>
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5344,17 +6279,17 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -5371,8 +6306,20 @@
       <c r="U96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5430,8 +6377,20 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5489,8 +6448,20 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5548,8 +6519,20 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -5580,11 +6563,11 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
-        <v>0</v>
-      </c>
-      <c r="N100" s="3">
-        <v>0</v>
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
@@ -5592,11 +6575,11 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
+      <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
+        <v>0</v>
       </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
@@ -5607,16 +6590,28 @@
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3">
+        <v>0</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>3</v>
@@ -5639,17 +6634,17 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -5666,8 +6661,20 @@
       <c r="U101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V101" s="3">
+        <v>0</v>
+      </c>
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -5684,10 +6691,10 @@
         <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="I102" s="3">
-        <v>0</v>
+        <v>-700</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
@@ -5704,17 +6711,17 @@
       <c r="N102" s="3">
         <v>0</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
+      <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q102" s="3">
+        <v>0</v>
+      </c>
+      <c r="R102" s="3">
+        <v>0</v>
       </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
@@ -5723,6 +6730,18 @@
         <v>3</v>
       </c>
       <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
